--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487957_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487957_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7107</v>
+        <v>6.1117</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9577</v>
+        <v>3.1449</v>
       </c>
       <c r="F2" t="n">
-        <v>3.753</v>
+        <v>2.9668</v>
       </c>
       <c r="G2" t="n">
         <v>1.703</v>
@@ -610,13 +610,13 @@
         <v>0.7929</v>
       </c>
       <c r="S2" t="n">
-        <v>1.858</v>
+        <v>1.259</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7564</v>
+        <v>0.9435</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1016</v>
+        <v>0.3154</v>
       </c>
       <c r="V2" t="n">
         <v>2.555</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3796</v>
+        <v>5.4701</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9649</v>
+        <v>4.0273</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4148</v>
+        <v>1.4428</v>
       </c>
       <c r="G3" t="n">
         <v>2.5027</v>
@@ -688,13 +688,13 @@
         <v>1.784</v>
       </c>
       <c r="S3" t="n">
-        <v>0.54</v>
+        <v>0.6304</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8077</v>
+        <v>0.8701</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2678</v>
+        <v>-0.2397</v>
       </c>
       <c r="V3" t="n">
         <v>1.5441</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.6029</v>
+        <v>4.9918</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7069</v>
+        <v>4.8712</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1041</v>
+        <v>0.1206</v>
       </c>
       <c r="G4" t="n">
         <v>1.1823</v>
@@ -766,13 +766,13 @@
         <v>1.784</v>
       </c>
       <c r="S4" t="n">
-        <v>0.359</v>
+        <v>0.7479</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8077</v>
+        <v>0.972</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4487</v>
+        <v>-0.2241</v>
       </c>
       <c r="V4" t="n">
         <v>1.2775</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. ÁVALOS ORTIZ</t>
+          <t>R. REVELLES DIAZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9053</v>
+        <v>0.9111</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9053</v>
+        <v>0.2587</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.6525</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9053</v>
+        <v>-1.7232</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3027</v>
+        <v>-1.155</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6027</v>
+        <v>-0.5682</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9053</v>
+        <v>-1.1449</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3027</v>
+        <v>-0.4295</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6027</v>
+        <v>-0.7154</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-0.5782</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.7255</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.1472</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.3947</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.2956</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.5441</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. AVALOS ORTIZ</t>
+          <t>P. ÁVALOS ORTIZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4939</v>
+        <v>0.9053</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6199</v>
+        <v>0.9053</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.126</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7472</v>
+        <v>0.9053</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4971</v>
+        <v>0.3027</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7499</v>
+        <v>0.6027</v>
       </c>
       <c r="J7" t="n">
-        <v>1.925</v>
+        <v>0.9053</v>
       </c>
       <c r="K7" t="n">
-        <v>2.5562</v>
+        <v>0.3027</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6312</v>
+        <v>0.6027</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1779</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0591</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1187</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9911</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1893</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1805</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0331</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5581</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.525</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2775</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.674</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. REVELLES DIAZ</t>
+          <t>P. AVALOS ORTIZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4141</v>
+        <v>0.7976</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0699</v>
+        <v>0.6428</v>
       </c>
       <c r="F8" t="n">
-        <v>0.484</v>
+        <v>0.1548</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7232</v>
+        <v>0.7472</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.155</v>
+        <v>1.4971</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5682</v>
+        <v>-0.7499</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1449</v>
+        <v>1.925</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4295</v>
+        <v>2.5562</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7154</v>
+        <v>-0.6312</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5782</v>
+        <v>-1.1779</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7255</v>
+        <v>-1.0591</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1472</v>
+        <v>-0.1187</v>
       </c>
       <c r="P8" t="n">
         <v>0.9911</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1982</v>
+        <v>-1.1893</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1893</v>
+        <v>2.1805</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3979</v>
+        <v>0.3368</v>
       </c>
       <c r="T8" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4641</v>
+        <v>-0.2442</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5441</v>
+        <v>-1.2775</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2071</v>
+        <v>-0.674</v>
       </c>
       <c r="X8" t="n">
-        <v>0.337</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="9">
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. VALEIRAS CREUS</t>
+          <t>L. SIGISMONTI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1998</v>
+        <v>-0.3664</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8186</v>
+        <v>-0.2588</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6188</v>
+        <v>-0.1076</v>
       </c>
       <c r="G10" t="n">
-        <v>1.5714</v>
+        <v>-0.2986</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5364</v>
+        <v>-0.5876</v>
       </c>
       <c r="I10" t="n">
-        <v>1.035</v>
+        <v>0.289</v>
       </c>
       <c r="J10" t="n">
-        <v>3.6302</v>
+        <v>0.2565</v>
       </c>
       <c r="K10" t="n">
-        <v>2.3406</v>
+        <v>1.0769</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2896</v>
+        <v>-0.8204</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.0588</v>
+        <v>-0.5551</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.8042</v>
+        <v>-1.6645</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2545</v>
+        <v>1.1094</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.7751</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.9556</v>
+        <v>-2.1805</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1805</v>
+        <v>1.5858</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2705</v>
+        <v>1.4674</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5068</v>
+        <v>1.7356</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7637</v>
+        <v>-0.2682</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2666</v>
+        <v>-0.9405</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.0704</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2666</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. LOPEZ PERAGON</t>
+          <t>P. TRUNO SOMS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7118</v>
+        <v>-0.4475</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7305</v>
+        <v>-0.7654</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0187</v>
+        <v>0.3179</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6791</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-1.16</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6791</v>
+        <v>0.3883</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6791</v>
+        <v>-0.1354</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.3027</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6791</v>
+        <v>-0.4381</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>-0.6363</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-1.4627</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.8264</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.1805</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0326</v>
+        <v>0.1082</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0514</v>
+        <v>0.3434</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0187</v>
+        <v>-0.2351</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRIGUEZ</t>
+          <t>M. LOPEZ PERAGON</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.7678</v>
+        <v>-0.6213</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.6681</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2199</v>
+        <v>0.0468</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2986</v>
+        <v>-0.6791</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5876</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.289</v>
+        <v>-0.6791</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2565</v>
+        <v>-0.6791</v>
       </c>
       <c r="K12" t="n">
-        <v>1.0769</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.8204</v>
+        <v>-0.6791</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5551</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.6645</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.1094</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.5947</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.1805</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.066</v>
+        <v>0.0578</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4465</v>
+        <v>0.011</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3805</v>
+        <v>0.0468</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9405</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.0704</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.8701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. TRUNO SOMS</t>
+          <t>D. JIMENEZ EXPOSITO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.8883</v>
+        <v>-0.6896</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.0939</v>
+        <v>-0.7048</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2056</v>
+        <v>0.0152</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-0.7909</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.16</v>
+        <v>-0.7909</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3883</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1354</v>
+        <v>-0.659</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3027</v>
+        <v>-0.659</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.4381</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6363</v>
+        <v>-0.1319</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.4627</v>
+        <v>-0.1319</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8264</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9911</v>
+        <v>0.7929</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.1805</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1893</v>
+        <v>0.7929</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3326</v>
+        <v>-0.0881</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0148</v>
+        <v>-0.0459</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3474</v>
+        <v>-0.0422</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2071</v>
+        <v>-0.6036</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. JIMENEZ EXPOSITO</t>
+          <t>J. VALEIRAS CREUS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.9495</v>
+        <v>-0.7499</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.9085</v>
+        <v>-0.8352000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0409</v>
+        <v>0.0853</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.7909</v>
+        <v>1.5714</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7909</v>
+        <v>0.5364</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1.035</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.659</v>
+        <v>3.6302</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.659</v>
+        <v>2.3406</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.2896</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1319</v>
+        <v>-2.0588</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1319</v>
+        <v>-1.8042</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>-0.2545</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7929</v>
+        <v>-2.7751</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-4.9556</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7929</v>
+        <v>2.1805</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.348</v>
+        <v>0.7204</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2496</v>
+        <v>0.4902</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0984</v>
+        <v>0.2302</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6036</v>
+        <v>-0.2666</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6036</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.0422</v>
+        <v>-3.1179</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.8912</v>
+        <v>-1.2758</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.151</v>
+        <v>-1.8421</v>
       </c>
       <c r="G15" t="n">
         <v>-1.1895</v>
@@ -1624,13 +1624,13 @@
         <v>1.3876</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9402</v>
+        <v>0.8645</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4868</v>
+        <v>1.1023</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5466</v>
+        <v>-0.2378</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2071</v>
@@ -1657,16 +1657,16 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>13.7578</v>
+        <v>15.0057</v>
       </c>
       <c r="E16" t="n">
-        <v>9.9049</v>
+        <v>11.1528</v>
       </c>
       <c r="F16" t="n">
-        <v>3.853000000000001</v>
+        <v>3.853</v>
       </c>
       <c r="G16" t="n">
-        <v>4.969600000000001</v>
+        <v>4.9696</v>
       </c>
       <c r="H16" t="n">
         <v>0.3298999999999996</v>
@@ -1693,7 +1693,7 @@
         <v>6.226299999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>-6.661338147750939e-16</v>
+        <v>-1.110223024625157e-15</v>
       </c>
       <c r="Q16" t="n">
         <v>-14.8667</v>
@@ -1702,10 +1702,10 @@
         <v>14.8668</v>
       </c>
       <c r="S16" t="n">
-        <v>4.9557</v>
+        <v>6.2034</v>
       </c>
       <c r="T16" t="n">
-        <v>6.149999999999999</v>
+        <v>7.398</v>
       </c>
       <c r="U16" t="n">
         <v>-1.1945</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. LOPEZ MUÑOZ</t>
+          <t>A. SEARA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6052999999999999</v>
+        <v>1.0786</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6052999999999999</v>
+        <v>1.8262</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-0.7477</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6052999999999999</v>
+        <v>-2.5254</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6052999999999999</v>
+        <v>-0.2584</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-2.2671</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6052999999999999</v>
+        <v>-0.3676</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6052999999999999</v>
+        <v>2.3412</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-2.7087</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-2.1579</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-2.5996</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>0.4417</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.5947</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.1805</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.7751</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-1.2407</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.1172</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-1.1235</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>4.4914</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2414</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. PERALES FERNANDEZ</t>
+          <t>V. CHERNODOLIA SANZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4602</v>
+        <v>0.8449</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9112</v>
+        <v>0.8753</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.451</v>
+        <v>-0.0304</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.8963</v>
+        <v>2.6722</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0979</v>
+        <v>-0.0542</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.7984</v>
+        <v>2.7264</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7124</v>
+        <v>3.7142</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5655</v>
+        <v>1.4124</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2779</v>
+        <v>2.3018</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1839</v>
+        <v>-1.042</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6634</v>
+        <v>-1.4666</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5205</v>
+        <v>0.4246</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1893</v>
+        <v>-2.1805</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-4.1627</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1893</v>
+        <v>1.9822</v>
       </c>
       <c r="S18" t="n">
-        <v>1.7456</v>
+        <v>-0.3459</v>
       </c>
       <c r="T18" t="n">
-        <v>1.4868</v>
+        <v>0.1167</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2587</v>
+        <v>-0.4626</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5784</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1367</v>
+        <v>1.2071</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.7151</v>
+        <v>-0.508</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. FURLAN</t>
+          <t>J. LOPEZ MUÑOZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0114</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>2.8605</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.8719</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>2.4596</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5936</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.134</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>4.0239</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>4.0563</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0324</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5643</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4627</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1016</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7929</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.784</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0458</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2351</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.2809</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.218</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.4074</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.8107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ</t>
+          <t>P. PERALES FERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0693</v>
+        <v>0.1592</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.022</v>
+        <v>1.1981</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0472</v>
+        <v>-1.0389</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0256</v>
+        <v>-1.8963</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1614</v>
+        <v>-0.0979</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1358</v>
+        <v>-1.7984</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0404</v>
+        <v>-0.7124</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0404</v>
+        <v>0.5655</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-1.2779</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.066</v>
+        <v>-1.1839</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2018</v>
+        <v>-0.6634</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1358</v>
+        <v>-0.5205</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0437</v>
+        <v>1.4445</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0624</v>
+        <v>0.7738</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0187</v>
+        <v>0.6708</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.5784</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.1367</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.7151</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. SEARA RODRIGUEZ</t>
+          <t>L. FURLAN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1439</v>
+        <v>-0.0173</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0113</v>
+        <v>2.5549</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1551</v>
+        <v>-2.5722</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.5254</v>
+        <v>2.4596</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2584</v>
+        <v>2.5936</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.2671</v>
+        <v>-0.134</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3676</v>
+        <v>4.0239</v>
       </c>
       <c r="K21" t="n">
-        <v>2.3412</v>
+        <v>4.0563</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.7087</v>
+        <v>-0.0324</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.1579</v>
+        <v>-1.5643</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.5996</v>
+        <v>-1.4627</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4417</v>
+        <v>-0.1016</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5947</v>
+        <v>0.7929</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1805</v>
+        <v>-0.9911</v>
       </c>
       <c r="R21" t="n">
-        <v>2.7751</v>
+        <v>1.784</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.4631</v>
+        <v>-1.0517</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9322</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.531</v>
+        <v>-0.9812</v>
       </c>
       <c r="V21" t="n">
-        <v>4.25</v>
+        <v>-2.218</v>
       </c>
       <c r="W21" t="n">
-        <v>4.4914</v>
+        <v>-0.4074</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2414</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. VALOR LARA</t>
+          <t>M. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3061</v>
+        <v>-0.0412</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5547</v>
+        <v>-0.022</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2486</v>
+        <v>-0.0192</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7088</v>
+        <v>-0.0256</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5403</v>
+        <v>-0.1614</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1685</v>
+        <v>0.1358</v>
       </c>
       <c r="J22" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.0404</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.0127</v>
+        <v>0.0404</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0804</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7765</v>
+        <v>-0.066</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5276</v>
+        <v>-0.2018</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2488</v>
+        <v>0.1358</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.784</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1893</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.1867</v>
+        <v>-0.0156</v>
       </c>
       <c r="T22" t="n">
-        <v>1.351</v>
+        <v>-0.0624</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8357</v>
+        <v>0.0468</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. CABRERA SALMON</t>
+          <t>I. POYATOS GARCIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3889</v>
+        <v>-0.453</v>
       </c>
       <c r="E23" t="n">
-        <v>1.4185</v>
+        <v>-1.1893</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8074</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6139</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.2604</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6465</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6862</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6059</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0804</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3001</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.8662</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5661</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.5858</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.1982</v>
+        <v>-1.1893</v>
       </c>
       <c r="R23" t="n">
-        <v>1.784</v>
+        <v>0.1982</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7617</v>
+        <v>-0.1358</v>
       </c>
       <c r="T23" t="n">
-        <v>1.6044</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8427</v>
+        <v>-0.1358</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.1225</v>
+        <v>0.674</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.674</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.4485</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>I. POYATOS GARCIA</t>
+          <t>T. YOME</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.453</v>
+        <v>-0.5125</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.1893</v>
+        <v>-0.515</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7364000000000001</v>
+        <v>0.0025</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.8655</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>-0.1148</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1.1004</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1.7756</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>-0.6752</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>-0.2349</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>-0.7953</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>0.5604</v>
       </c>
       <c r="P24" t="n">
+        <v>0.1982</v>
+      </c>
+      <c r="Q24" t="n">
         <v>-0.9911</v>
       </c>
-      <c r="Q24" t="n">
-        <v>-1.1893</v>
-      </c>
       <c r="R24" t="n">
-        <v>0.1982</v>
+        <v>1.1893</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1358</v>
+        <v>-0.0321</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>0.0496</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1358</v>
+        <v>-0.0818</v>
       </c>
       <c r="V24" t="n">
-        <v>0.674</v>
+        <v>-1.5441</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="X24" t="n">
-        <v>0.674</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>V. CHERNODOLIA SANZ</t>
+          <t>A. VALOR LARA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5447</v>
+        <v>-1.4521</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0415</v>
+        <v>-2.4715</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5032</v>
+        <v>1.0194</v>
       </c>
       <c r="G25" t="n">
-        <v>2.6722</v>
+        <v>-0.7088</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0542</v>
+        <v>-0.5403</v>
       </c>
       <c r="I25" t="n">
-        <v>2.7264</v>
+        <v>-0.1685</v>
       </c>
       <c r="J25" t="n">
-        <v>3.7142</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>1.4124</v>
+        <v>-0.0127</v>
       </c>
       <c r="L25" t="n">
-        <v>2.3018</v>
+        <v>0.0804</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.042</v>
+        <v>-0.7765</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.4666</v>
+        <v>-0.5276</v>
       </c>
       <c r="O25" t="n">
-        <v>0.4246</v>
+        <v>-0.2488</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.1805</v>
+        <v>-1.784</v>
       </c>
       <c r="Q25" t="n">
-        <v>-4.1627</v>
+        <v>-2.9733</v>
       </c>
       <c r="R25" t="n">
-        <v>1.9822</v>
+        <v>1.1893</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.7355</v>
+        <v>1.0407</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8001</v>
+        <v>0.4342</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9354</v>
+        <v>0.6065</v>
       </c>
       <c r="V25" t="n">
-        <v>0.6991000000000001</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.508</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.4938</v>
+        <v>-1.469</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.7767</v>
+        <v>-1.4711</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2829</v>
+        <v>0.0021</v>
       </c>
       <c r="G26" t="n">
         <v>-1.0583</v>
@@ -2482,13 +2482,13 @@
         <v>0.3964</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5654</v>
+        <v>-0.5405</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4992</v>
+        <v>-0.1936</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.347</v>
       </c>
       <c r="V26" t="n">
         <v>-0.2666</v>
@@ -2503,7 +2503,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>T. YOME</t>
+          <t>S. CABRERA SALMON</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.6246</v>
+        <v>-1.659</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.1263</v>
+        <v>0.2979</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.4984</v>
+        <v>-1.9569</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8655</v>
+        <v>-0.6139</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9802999999999999</v>
+        <v>-1.2604</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1148</v>
+        <v>0.6465</v>
       </c>
       <c r="J27" t="n">
-        <v>1.1004</v>
+        <v>0.6862</v>
       </c>
       <c r="K27" t="n">
-        <v>1.7756</v>
+        <v>0.6059</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.6752</v>
+        <v>0.0804</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.2349</v>
+        <v>-1.3001</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.7953</v>
+        <v>-1.8662</v>
       </c>
       <c r="O27" t="n">
-        <v>0.5604</v>
+        <v>0.5661</v>
       </c>
       <c r="P27" t="n">
-        <v>0.1982</v>
+        <v>1.5858</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.9911</v>
+        <v>-0.1982</v>
       </c>
       <c r="R27" t="n">
-        <v>1.1893</v>
+        <v>1.784</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.1442</v>
+        <v>-0.5084</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.5616</v>
+        <v>0.4838</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.5826</v>
+        <v>-0.9922</v>
       </c>
       <c r="V27" t="n">
-        <v>-1.5441</v>
+        <v>-2.1225</v>
       </c>
       <c r="W27" t="n">
         <v>-0.674</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.8701</v>
+        <v>-1.4485</v>
       </c>
     </row>
     <row r="28">
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-3.7773</v>
+        <v>-3.4939</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.0398</v>
+        <v>-1.836</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.7375</v>
+        <v>-1.6578</v>
       </c>
       <c r="G28" t="n">
         <v>-1.7355</v>
@@ -2638,13 +2638,13 @@
         <v>0.1982</v>
       </c>
       <c r="S28" t="n">
-        <v>-1.2488</v>
+        <v>-0.9654</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.4368</v>
+        <v>-0.233</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.8121</v>
+        <v>-0.7324000000000001</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-6.0104</v>
+        <v>-5.3103</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.9094</v>
+        <v>-3.7056</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.101</v>
+        <v>-1.6047</v>
       </c>
       <c r="G29" t="n">
         <v>-3.0083</v>
@@ -2716,13 +2716,13 @@
         <v>2.1805</v>
       </c>
       <c r="S29" t="n">
-        <v>-1.2671</v>
+        <v>-0.5671</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.1906</v>
+        <v>0.0131</v>
       </c>
       <c r="U29" t="n">
-        <v>-1.0765</v>
+        <v>-0.5802</v>
       </c>
       <c r="V29" t="n">
         <v>-2.726</v>
@@ -2749,31 +2749,31 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-13.7579</v>
+        <v>-11.7203</v>
       </c>
       <c r="E30" t="n">
-        <v>-3.8529</v>
+        <v>-3.852799999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>-9.904800000000002</v>
+        <v>-7.867400000000001</v>
       </c>
       <c r="G30" t="n">
         <v>-4.9695</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.3298000000000001</v>
+        <v>-0.3298000000000008</v>
       </c>
       <c r="I30" t="n">
         <v>-4.639900000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>5.413200000000002</v>
+        <v>5.4132</v>
       </c>
       <c r="K30" t="n">
         <v>11.6395</v>
       </c>
       <c r="L30" t="n">
-        <v>-6.226000000000001</v>
+        <v>-6.225999999999999</v>
       </c>
       <c r="M30" t="n">
         <v>-10.3829</v>
@@ -2785,7 +2785,7 @@
         <v>1.5863</v>
       </c>
       <c r="P30" t="n">
-        <v>-9.999999999965592e-05</v>
+        <v>-9.999999999998899e-05</v>
       </c>
       <c r="Q30" t="n">
         <v>-14.8666</v>
@@ -2794,13 +2794,13 @@
         <v>14.8665</v>
       </c>
       <c r="S30" t="n">
-        <v>-4.9554</v>
+        <v>-2.918</v>
       </c>
       <c r="T30" t="n">
-        <v>1.1944</v>
+        <v>1.1945</v>
       </c>
       <c r="U30" t="n">
-        <v>-6.1501</v>
+        <v>-4.1126</v>
       </c>
       <c r="V30" t="n">
         <v>-3.8325</v>
